--- a/output/J3R-MC-YDAF_20261008_165619/mandatory_fields_report.xlsx
+++ b/output/J3R-MC-YDAF_20261008_165619/mandatory_fields_report.xlsx
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>593</v>
+        <v>614</v>
       </c>
       <c r="G129" t="n">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>600</v>
+        <v>623</v>
       </c>
       <c r="G130" t="n">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>593</v>
+        <v>614</v>
       </c>
       <c r="G131" t="n">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -5568,10 +5568,10 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>600</v>
+        <v>623</v>
       </c>
       <c r="G132" t="n">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
